--- a/output/P5.xlsx
+++ b/output/P5.xlsx
@@ -2853,15 +2853,16 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Base directory for this skill: /tmp/claude-1000/bundled-skills/2.1.239/2756c3bfb8a17ef74f8c4a620fe0ae50/dataviz
 # Data Visualization
@@ -2961,7 +2962,6 @@
 | `scripts/validate_palette.js` | Runnable six-checks validator (run it; don't eyeball) |</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
